--- a/Новая таблица 44 1.xlsx
+++ b/Новая таблица 44 1.xlsx
@@ -23,46 +23,98 @@
     <t>Сумма</t>
   </si>
   <si>
-    <t>Сумма для 2</t>
-  </si>
-  <si>
-    <t>Сумма для 3</t>
+    <t>максимальный показатель</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="XO Thames"/>
+        <b val="true"/>
+        <sz val="10"/>
+      </rPr>
+      <t>сумма для 2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="XO Thames"/>
+        <b val="true"/>
+        <sz val="10"/>
+      </rPr>
+      <t>сумма для 3</t>
+    </r>
+  </si>
+  <si/>
+  <si>
+    <t>1,5691Е+10</t>
+  </si>
+  <si>
+    <t>4,7072Е+10</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="XO Thames"/>
+        <b val="true"/>
+        <sz val="10"/>
+      </rPr>
+      <t>статистическая функция</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="XO Thames"/>
+        <b val="true"/>
+        <sz val="10"/>
+      </rPr>
+      <t>для А (лист 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="XO Thames"/>
+        <b val="true"/>
+        <sz val="10"/>
+      </rPr>
+      <t>для В ( лист 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <rFont val="XO Thames"/>
+        <b val="true"/>
+        <sz val="10"/>
+      </rPr>
+      <t>для С ( лист 3)</t>
+    </r>
+  </si>
+  <si>
+    <t>среднее значение</t>
+  </si>
+  <si>
+    <t>максимальное значение</t>
+  </si>
+  <si>
+    <t>минимальное значение</t>
+  </si>
+  <si>
+    <t>медиана</t>
+  </si>
+  <si>
+    <t>мода</t>
+  </si>
+  <si>
+    <t>дисперсия</t>
   </si>
   <si>
     <r>
       <t xml:space="preserve">
 </t>
     </r>
-  </si>
-  <si>
-    <t>Статистическая функция</t>
-  </si>
-  <si>
-    <t>Для А (лист 3)</t>
-  </si>
-  <si>
-    <t>Для В (лист 3)</t>
-  </si>
-  <si>
-    <t>Для С (лист3)</t>
-  </si>
-  <si>
-    <t>Среднее значение</t>
-  </si>
-  <si>
-    <t>Минимальное значение</t>
-  </si>
-  <si>
-    <t>Максимальное значение</t>
-  </si>
-  <si>
-    <t>Медиана</t>
-  </si>
-  <si>
-    <t>Мода</t>
-  </si>
-  <si>
-    <t>Дисперсия</t>
   </si>
   <si>
     <t>Колледж 1</t>
@@ -81,7 +133,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:a15="http://schemas.microsoft.com/office/drawing/2012/main" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:co="http://ncloudtech.com" xmlns:co-ooxml="http://ncloudtech.com/ooxml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:p="http://schemas.openxmlformats.org/presentationml/2006/main" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:s="http://schemas.openxmlformats.org/officeDocument/2006/sharedTypes" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:v="urn:schemas-microsoft-com:vml" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main" xmlns:w10="urn:schemas-microsoft-com:office:word" xmlns:w14="http://schemas.microsoft.com/office/word/2010/wordml" xmlns:w15="http://schemas.microsoft.com/office/word/2012/wordml" xmlns:wp="http://schemas.openxmlformats.org/drawingml/2006/wordprocessingDrawing" xmlns:wpg="http://schemas.microsoft.com/office/word/2010/wordprocessingGroup" xmlns:wps="http://schemas.microsoft.com/office/word/2010/wordprocessingShape" xmlns:x="urn:schemas-microsoft-com:office:excel" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" mc:Ignorable="co co-ooxml w14 x14 w15">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <sz val="11"/>
@@ -94,6 +146,15 @@
       <name val="Liberation Sans"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="XO Thames"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="XO Thames"/>
+      <b val="true"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -103,7 +164,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -139,11 +200,25 @@
         <color rgb="000000" tint="0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="000000" tint="0"/>
+      </left>
+      <right style="thin">
+        <color rgb="000000" tint="0"/>
+      </right>
+      <top style="thin">
+        <color rgb="000000" tint="0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="000000" tint="0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf applyBorder="false" applyFill="false" applyFont="true" borderId="0" fillId="0" fontId="1" numFmtId="0" quotePrefix="false"/>
     <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" borderId="1" fillId="0" fontId="2" numFmtId="0" quotePrefix="false">
       <alignment horizontal="left" indent="1" vertical="center"/>
@@ -151,8 +226,14 @@
     <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" borderId="1" fillId="0" fontId="2" numFmtId="0" quotePrefix="false">
       <alignment horizontal="right" indent="1" vertical="center"/>
     </xf>
-    <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" applyNumberFormat="true" borderId="2" fillId="0" fontId="2" numFmtId="16" quotePrefix="false">
-      <alignment horizontal="left" indent="1" vertical="center"/>
+    <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" borderId="2" fillId="0" fontId="3" numFmtId="0" quotePrefix="false">
+      <alignment horizontal="left" indent="1" vertical="bottom"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" borderId="2" fillId="0" fontId="4" numFmtId="0" quotePrefix="false">
+      <alignment horizontal="left" indent="1" vertical="bottom"/>
+    </xf>
+    <xf applyAlignment="true" applyBorder="true" applyFill="false" applyFont="true" borderId="3" fillId="0" fontId="3" numFmtId="0" quotePrefix="false">
+      <alignment horizontal="right" indent="1" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -686,7 +767,8 @@
   <dimension ref="A1:Z300"/>
   <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="10.788470377394527" defaultRowHeight="15" zeroHeight="false"/>
   <cols>
-    <col bestFit="true" customWidth="true" max="16384" min="1" outlineLevel="0" style="0" width="10.788470377394527"/>
+    <col customWidth="true" max="1" min="1" outlineLevel="0" style="0" width="21.552104452673817"/>
+    <col bestFit="true" customWidth="true" max="16384" min="2" outlineLevel="0" style="0" width="10.788470377394527"/>
   </cols>
   <sheetData>
     <row outlineLevel="0" r="1">
@@ -1169,281 +1251,285 @@
   <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="10.788470377394527" defaultRowHeight="15" zeroHeight="false"/>
   <cols>
     <col customWidth="true" max="2" min="1" outlineLevel="0" width="16.496673262456088"/>
+    <col customWidth="true" max="3" min="3" outlineLevel="0" width="15.565408019525837"/>
   </cols>
   <sheetData>
     <row outlineLevel="0" r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="2">
+      <c r="A2" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="3">
+      <c r="A3" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="4">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="B4" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="5">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-    </row>
-    <row outlineLevel="0" r="2">
-      <c r="A2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
+      <c r="B5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row outlineLevel="0" r="6">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="3">
-      <c r="A3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="4">
-      <c r="A4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="5">
-      <c r="A5" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row outlineLevel="0" r="6">
-      <c r="A6" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
+      <c r="B6" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>121</v>
       </c>
     </row>
     <row outlineLevel="0" r="7">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
+      <c r="B7" s="5" t="n">
+        <v>63</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>364</v>
       </c>
     </row>
     <row outlineLevel="0" r="8">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>4</v>
+      <c r="B8" s="5" t="n">
+        <v>127</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>1093</v>
       </c>
     </row>
     <row outlineLevel="0" r="9">
-      <c r="A9" s="2" t="n">
+      <c r="A9" s="5" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>4</v>
+      <c r="B9" s="5" t="n">
+        <v>255</v>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>3280</v>
       </c>
     </row>
     <row outlineLevel="0" r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="5" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>4</v>
+      <c r="B10" s="5" t="n">
+        <v>511</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>9841</v>
       </c>
     </row>
     <row outlineLevel="0" r="11">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="5" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>4</v>
+      <c r="B11" s="5" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>29524</v>
       </c>
     </row>
     <row outlineLevel="0" r="12">
-      <c r="A12" s="2" t="n">
+      <c r="A12" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>4</v>
+      <c r="B12" s="5" t="n">
+        <v>2047</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>88573</v>
       </c>
     </row>
     <row outlineLevel="0" r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" s="5" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>4</v>
+      <c r="B13" s="5" t="n">
+        <v>4095</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>265720</v>
       </c>
     </row>
     <row outlineLevel="0" r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" s="5" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>4</v>
+      <c r="B14" s="5" t="n">
+        <v>8191</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>797161</v>
       </c>
     </row>
     <row outlineLevel="0" r="15">
-      <c r="A15" s="2" t="n">
+      <c r="A15" s="5" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>4</v>
+      <c r="B15" s="5" t="n">
+        <v>16383</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2391484</v>
       </c>
     </row>
     <row outlineLevel="0" r="16">
-      <c r="A16" s="2" t="n">
+      <c r="A16" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>4</v>
+      <c r="B16" s="5" t="n">
+        <v>32767</v>
+      </c>
+      <c r="C16" s="5" t="n">
+        <v>7174453</v>
       </c>
     </row>
     <row outlineLevel="0" r="17">
-      <c r="A17" s="2" t="n">
+      <c r="A17" s="5" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>4</v>
+      <c r="B17" s="5" t="n">
+        <v>65535</v>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>21523360</v>
       </c>
     </row>
     <row outlineLevel="0" r="18">
-      <c r="A18" s="2" t="n">
+      <c r="A18" s="5" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>4</v>
+      <c r="B18" s="5" t="n">
+        <v>131071</v>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>64570081</v>
       </c>
     </row>
     <row outlineLevel="0" r="19">
-      <c r="A19" s="2" t="n">
+      <c r="A19" s="5" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>4</v>
+      <c r="B19" s="5" t="n">
+        <v>262143</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>193710244</v>
       </c>
     </row>
     <row outlineLevel="0" r="20">
-      <c r="A20" s="2" t="n">
+      <c r="A20" s="5" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>4</v>
+      <c r="B20" s="5" t="n">
+        <v>524287</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>581130733</v>
       </c>
     </row>
     <row outlineLevel="0" r="21">
-      <c r="A21" s="2" t="n">
+      <c r="A21" s="5" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>4</v>
+      <c r="B21" s="5" t="n">
+        <v>1048575</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>1743392200</v>
       </c>
     </row>
     <row outlineLevel="0" r="22">
-      <c r="A22" s="2" t="n">
+      <c r="A22" s="5" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>4</v>
+      <c r="B22" s="5" t="n">
+        <v>2097151</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>5230176601</v>
       </c>
     </row>
     <row outlineLevel="0" r="23">
-      <c r="A23" s="2" t="n">
+      <c r="A23" s="5" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>4</v>
+      <c r="B23" s="5" t="n">
+        <v>4194303</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>6</v>
       </c>
     </row>
     <row outlineLevel="0" r="24">
-      <c r="A24" s="2" t="n">
+      <c r="A24" s="5" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>4</v>
+      <c r="B24" s="5" t="n">
+        <v>8388607</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>7</v>
       </c>
     </row>
     <row outlineLevel="0" r="25">
-      <c r="A25" s="2" t="n">
+      <c r="A25" s="5" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>4</v>
+      <c r="B25" s="5" t="n">
+        <v>16777215</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>141214768240</v>
       </c>
     </row>
   </sheetData>
@@ -1461,104 +1547,105 @@
   <sheetFormatPr baseColWidth="8" customHeight="false" defaultColWidth="10.788470377394527" defaultRowHeight="15" zeroHeight="false"/>
   <cols>
     <col customWidth="true" max="1" min="1" outlineLevel="0" width="19.689576673472221"/>
+    <col customWidth="true" max="4" min="4" outlineLevel="0" width="12.214631961209518"/>
   </cols>
   <sheetData>
     <row outlineLevel="0" r="1">
-      <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row outlineLevel="0" r="2">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="3" t="n">
-        <v>46153</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="5" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="C2" s="5" t="n">
+        <v>1398100.25</v>
+      </c>
+      <c r="D2" s="5" t="n">
+        <v>6775456051.40909</v>
       </c>
     </row>
     <row outlineLevel="0" r="3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>4</v>
+      <c r="A3" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="C3" s="5" t="n">
+        <v>1458887.17391304</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>7098096815.7142897</v>
       </c>
     </row>
     <row outlineLevel="0" r="4">
-      <c r="A4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>4</v>
+      <c r="A4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="C4" s="5" t="n">
+        <v>1525200.0909090899</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>7453001656.3000002</v>
       </c>
     </row>
     <row outlineLevel="0" r="5">
-      <c r="A5" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
+      <c r="A5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>1597828.33333333</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>7845264900.6842098</v>
       </c>
     </row>
     <row outlineLevel="0" r="6">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>4</v>
+      <c r="A6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>1677719</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>8281112948.5</v>
       </c>
     </row>
     <row outlineLevel="0" r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5" t="n">
         <v>14</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>4</v>
+      <c r="C7" s="5" t="n">
+        <v>1766018.36842105</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>8768237232.4705906</v>
       </c>
     </row>
   </sheetData>
@@ -1577,7 +1664,7 @@
   <sheetData>
     <row outlineLevel="0" r="1">
       <c r="A1" s="1" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="B1" s="2" t="n">
         <v>2021</v>
@@ -1603,7 +1690,7 @@
     </row>
     <row outlineLevel="0" r="2">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="n">
         <v>1510000</v>
@@ -1629,7 +1716,7 @@
     </row>
     <row outlineLevel="0" r="3">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="n">
         <v>237800</v>
@@ -1655,7 +1742,7 @@
     </row>
     <row outlineLevel="0" r="4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>3211400</v>
@@ -1681,7 +1768,7 @@
     </row>
     <row outlineLevel="0" r="5">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B5" s="2" t="n">
         <v>4961201</v>
